--- a/Vingapur/Справка_ППН_Vingapur.xlsx
+++ b/Vingapur/Справка_ППН_Vingapur.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J25"/>
+  <dimension ref="A2:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -538,169 +538,1437 @@
       </c>
     </row>
     <row r="12"/>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Комерция ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ЦНСНТ- 300/420 (база 480)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>НА-НВО Н-2/1 СО</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1221</v>
+      </c>
+      <c r="J14" t="n">
+        <v>61000284494</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Комерция ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ЦНСт- 300/480</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>НА-НВО Н-2/3 СО</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>193</v>
+      </c>
+      <c r="J15" t="n">
+        <v>61000294329</v>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Комерция ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ЦНС 60/198</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>НА-НВП Н-9/1 СО</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>31101</v>
+      </c>
+      <c r="J16" t="n">
+        <v>61000294458</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ЦНС 60/198</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>НА-НВП Н-9/3 СО</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>159</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>61000294459</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1Д630/125</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>НА-НПВ Н-13/1 СО</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8Ю8</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>61000294355</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1Д630-125-пкп-УХЛ3.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>НА-НПВ Н-13/4 СО</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>8Ю11</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>61000284370</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ДНС-2 Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1Д630/125</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>НА-НПВ- 2/1 СО</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>9ф3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>61000234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ДНС-2 Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1Д630/125</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>НА-НПВ- 2/2 СО</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>7д3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>61000490292</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ДНС-2 Новогоднее</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ЦНСт 60/264</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>НА-НВО-1 СО</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>61</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>61000294455</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ДНС-2 Новогоднее</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ЦНСт 105-294</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>НА-НВО-2 СО</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>3899</v>
+      </c>
+      <c r="J23" t="n">
+        <v>61000294570</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ДНС-2 Новогоднее</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ЦНС 60/264</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>НА-НВО-3 СО</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1064</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>61000294456</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ДНС-2 Новогоднее</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ЦНС 180/170</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>НА-НПВ-1 СО</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>105</v>
+      </c>
+      <c r="J25" t="n">
+        <v>61000222131</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ДНС-2 Новогоднее</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ЦНС 300/120</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>НА-НПВ-2 СО</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>61000436054</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ДНС-2 Новогоднее</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ЦНС 300/120</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>НА-НПВ-3 СО</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>140017</v>
+      </c>
+      <c r="J27" t="n">
+        <v>61000239763</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ДНС-2 Ярайнерское</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ЦНСнт 180-425-УХЛ5</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>НА-НВО Н-1 СО</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>98/128498</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>61000311991</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ДНС-2 Ярайнерское</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ЦНС 300-480</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>НА-НВО Н-2 СО</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>69</v>
+      </c>
+      <c r="J29" t="n">
+        <v>61000294406</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>17</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ДНС-2 Ярайнерское</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ЦНС 180-425</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>НА-НВО Н-3 СО</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>140219</v>
+      </c>
+      <c r="J30" t="n">
+        <v>61000234591</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>18</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ДНС-2 Ярайнерское</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ЦНСт 300-480</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>НА-НВО Н-4 СО</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1222</v>
+      </c>
+      <c r="J31" t="n">
+        <v>61000312053</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>19</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ДНС-2 Ярайнерское</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Д1250-125 </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>НА-НПВ Н-1 СО</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3л1</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>61000311957</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>20</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ДНС-2 Ярайнерское</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1Д630-125 </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>НА-НПВ Н-2 СО</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>10Б1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>61000536762</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>21</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ДНС-2 Ярайнерское</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1Д 1250-125 </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>НА-НПВ Н-3 СО</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>10у1</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>61000331531</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>22</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>транзитный насос к.5 Ярайнерское</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ЦНС 300-330</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>НА-ПН-1 СО</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>2159</v>
+      </c>
+      <c r="J35" t="n">
+        <v>61000506963</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>23</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>транзитный насос к.5 Ярайнерское</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ЦНС 300-180</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>НА-ПН-2 СО</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>82</v>
+      </c>
+      <c r="J36" t="n">
+        <v>61000294330</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>Работы по текущему ремонту</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>№ ЗАКАЗА САП ТОРО</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="C18" t="inlineStr">
+    <row r="40"/>
+    <row r="41">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Оборудование</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Марка оборудования</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Рег. №</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Зав №</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="42"/>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Комерция ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ЦНСНТ- 300/480 </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>НА-НВО Н-2/2 ТР</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>4141</v>
+      </c>
+      <c r="J44" t="n">
+        <v>61000314946</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Комерция ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ЦНСт 300-420 (база 480)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>НА-НВО Н-2/5 ТР</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>2768</v>
+      </c>
+      <c r="J45" t="n">
+        <v>61000284524</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ДНС-1 Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ЦНСт 180/170</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>НА-НВО-3 ТР</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>61000311951</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ДНС-1 Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1Д630/125 (подрез. 90)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>НА-НПВ-2/1 ТР</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>8Ю12</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>61000240709</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ДНС-1 Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ЦНСа 300/120</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>НА-НПВ-2/2 ТР</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>386</v>
+      </c>
+      <c r="J48" t="n">
+        <v>61000240714</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Работы по замене агрегатов</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>№ ЗАКАЗА САП ТОРО</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="C24" t="inlineStr">
+    <row r="51"/>
+    <row r="52">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Рег. №</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Монтаж/ПНР</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Марка оборудования</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="53"/>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Комерция ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>НА-НВО Н-2/4</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2767</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ЦНС- 300/420 (база 480)</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>61000284509</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Комерция ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>НА-НВО Н-2/4</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>2557</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ЦНСт 300-480</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>61000284499</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>НА-НПВ Н-13/2</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3417</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1Д630-125 УХЛ 3.1</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>61000294492</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>НА-Н-7/2</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2101</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>12НА 9х4</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>61000311877</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>НА-Н-7/2</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>2101</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>12НА 9х4</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>61000311877</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>6</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>НА-Н-16/1</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2756</v>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>12 НА 9х4</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>61000294526</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>7</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ЦППН-3</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ЦПС Вынгапуровское_ЯНАО</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>НА-Н-16/1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>2756</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>12 НА 9х4</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>61000294526</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="J39:J42"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="D52:D53"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="C24:C25"/>
     <mergeCell ref="D11:D12"/>
-    <mergeCell ref="I16:I19"/>
-    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="H50:H53"/>
     <mergeCell ref="H9:H12"/>
-    <mergeCell ref="F18:F19"/>
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="H5"/>
-    <mergeCell ref="I22:I25"/>
     <mergeCell ref="F4"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="H39:H42"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C39:G40"/>
     <mergeCell ref="C11:C12"/>
+    <mergeCell ref="F41:F42"/>
     <mergeCell ref="E11:E12"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="C52:C53"/>
     <mergeCell ref="B9:B12"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="J22:J25"/>
+    <mergeCell ref="I39:I42"/>
+    <mergeCell ref="F52:F53"/>
     <mergeCell ref="F3"/>
-    <mergeCell ref="H16:H19"/>
-    <mergeCell ref="J16:J19"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="J50:J53"/>
+    <mergeCell ref="G41:G42"/>
     <mergeCell ref="F11:F12"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="I50:I53"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="D6:I6"/>
     <mergeCell ref="F2"/>
     <mergeCell ref="I9:I12"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="C50:G51"/>
+    <mergeCell ref="A39:A42"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C22:G23"/>
-    <mergeCell ref="F24:F25"/>
     <mergeCell ref="C9:G10"/>
+    <mergeCell ref="E52:E53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
